--- a/GANTT_EMINEM.xlsx
+++ b/GANTT_EMINEM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0303A1D9-CB23-4451-859C-1A86EE335D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390858D1-B534-4ECF-8DC1-67EE5734D565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,9 +212,6 @@
     <t>Startbedingung programmieren</t>
   </si>
   <si>
-    <t>Startanzeige oder Countdown erstellen</t>
-  </si>
-  <si>
     <t>Fussballspieler zufällig zusweisen</t>
   </si>
   <si>
@@ -267,6 +264,9 @@
   </si>
   <si>
     <t>Weitere Eingaben nach spielende verhindern</t>
+  </si>
+  <si>
+    <t>Startanzeige oder Countdown erstellen. 3.2.1.go</t>
   </si>
 </sst>
 </file>
@@ -612,6 +612,81 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="15" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="16" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="18" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="12" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="9" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="10">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="10" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="10" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -621,86 +696,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="15" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="16" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="18" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="10" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="10" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="10" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="12" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="9" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="9" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -724,7 +724,7 @@
     <cellStyle name="Überschriften für Zeiträume" xfId="3" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="Zeitraumwert" xfId="13" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -854,15 +854,6 @@
         <bottom style="thin">
           <color theme="7"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="7"/>
-        </top>
         <vertical/>
         <horizontal/>
       </border>
@@ -1115,11 +1106,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="4.59765625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.46484375" style="36" customWidth="1"/>
+    <col min="2" max="2" width="21.46484375" style="26" customWidth="1"/>
     <col min="3" max="6" width="15.59765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.06640625" style="31" customWidth="1"/>
+    <col min="7" max="7" width="24.06640625" style="21" customWidth="1"/>
     <col min="8" max="8" width="4.59765625" style="1" customWidth="1"/>
-    <col min="9" max="19" width="4.59765625" style="1"/>
+    <col min="9" max="10" width="4.59765625" style="1"/>
+    <col min="11" max="11" width="4.86328125" style="1" customWidth="1"/>
+    <col min="12" max="19" width="4.59765625" style="1"/>
     <col min="20" max="20" width="6.46484375" style="1" customWidth="1"/>
     <col min="21" max="27" width="4.59765625" style="1"/>
     <col min="28" max="32" width="4.59765625" style="5"/>
@@ -1128,7 +1121,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:67" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="1.6">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4"/>
@@ -1138,7 +1131,7 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:67" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="6"/>
@@ -1152,72 +1145,72 @@
         <v>0</v>
       </c>
       <c r="J2" s="9"/>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="10" t="s">
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="16" t="s">
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="19"/>
-      <c r="AA2" s="16" t="s">
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="16" t="s">
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="39"/>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AJ2" s="17"/>
-      <c r="AK2" s="17"/>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="17"/>
-      <c r="AN2" s="17"/>
-      <c r="AO2" s="17"/>
-      <c r="AP2" s="17"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
     </row>
     <row r="3" spans="1:67" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="24"/>
+      <c r="I3" s="15"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1238,285 +1231,285 @@
       <c r="AA3" s="1"/>
     </row>
     <row r="4" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="35"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26">
+      <c r="B4" s="25"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="16">
         <v>1</v>
       </c>
-      <c r="I4" s="26">
-        <v>2</v>
-      </c>
-      <c r="J4" s="26">
+      <c r="I4" s="16">
+        <v>2</v>
+      </c>
+      <c r="J4" s="16">
         <v>3</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="16">
         <v>4</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="16">
         <v>5</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="16">
         <v>6</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="16">
         <v>7</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="16">
         <v>8</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="16">
         <v>9</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="16">
         <v>10</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="16">
         <v>11</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="16">
         <v>12</v>
       </c>
-      <c r="T4" s="26">
+      <c r="T4" s="16">
         <v>13</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="16">
         <v>14</v>
       </c>
-      <c r="V4" s="26">
+      <c r="V4" s="16">
         <v>15</v>
       </c>
-      <c r="W4" s="26">
+      <c r="W4" s="16">
         <v>16</v>
       </c>
-      <c r="X4" s="26">
+      <c r="X4" s="16">
         <v>17</v>
       </c>
-      <c r="Y4" s="26">
-        <v>18</v>
-      </c>
-      <c r="Z4" s="26">
+      <c r="Y4" s="16">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="16">
         <v>19</v>
       </c>
-      <c r="AA4" s="26">
+      <c r="AA4" s="16">
         <v>20</v>
       </c>
-      <c r="AB4" s="26">
+      <c r="AB4" s="16">
         <v>21</v>
       </c>
-      <c r="AC4" s="26">
+      <c r="AC4" s="16">
         <v>22</v>
       </c>
-      <c r="AD4" s="26">
+      <c r="AD4" s="16">
         <v>23</v>
       </c>
-      <c r="AE4" s="26">
+      <c r="AE4" s="16">
         <v>24</v>
       </c>
-      <c r="AF4" s="26">
+      <c r="AF4" s="16">
         <v>25</v>
       </c>
-      <c r="AG4" s="26">
+      <c r="AG4" s="16">
         <v>26</v>
       </c>
-      <c r="AH4" s="26">
+      <c r="AH4" s="16">
         <v>27</v>
       </c>
-      <c r="AI4" s="26">
+      <c r="AI4" s="16">
         <v>28</v>
       </c>
-      <c r="AJ4" s="26">
+      <c r="AJ4" s="16">
         <v>29</v>
       </c>
-      <c r="AK4" s="26">
+      <c r="AK4" s="16">
         <v>30</v>
       </c>
-      <c r="AL4" s="26">
+      <c r="AL4" s="16">
         <v>31</v>
       </c>
-      <c r="AM4" s="26">
+      <c r="AM4" s="16">
         <v>32</v>
       </c>
-      <c r="AN4" s="26">
+      <c r="AN4" s="16">
         <v>33</v>
       </c>
-      <c r="AO4" s="26">
+      <c r="AO4" s="16">
         <v>34</v>
       </c>
-      <c r="AP4" s="26">
+      <c r="AP4" s="16">
         <v>35</v>
       </c>
-      <c r="AQ4" s="26">
+      <c r="AQ4" s="16">
         <v>36</v>
       </c>
-      <c r="AR4" s="26">
+      <c r="AR4" s="16">
         <v>37</v>
       </c>
-      <c r="AS4" s="26">
+      <c r="AS4" s="16">
         <v>38</v>
       </c>
-      <c r="AT4" s="26">
+      <c r="AT4" s="16">
         <v>39</v>
       </c>
-      <c r="AU4" s="26">
+      <c r="AU4" s="16">
         <v>40</v>
       </c>
-      <c r="AV4" s="26">
+      <c r="AV4" s="16">
         <v>41</v>
       </c>
-      <c r="AW4" s="26">
+      <c r="AW4" s="16">
         <v>42</v>
       </c>
-      <c r="AX4" s="26">
+      <c r="AX4" s="16">
         <v>43</v>
       </c>
-      <c r="AY4" s="26">
+      <c r="AY4" s="16">
         <v>44</v>
       </c>
-      <c r="AZ4" s="26">
+      <c r="AZ4" s="16">
         <v>45</v>
       </c>
-      <c r="BA4" s="26">
+      <c r="BA4" s="16">
         <v>46</v>
       </c>
-      <c r="BB4" s="26">
+      <c r="BB4" s="16">
         <v>47</v>
       </c>
-      <c r="BC4" s="26">
+      <c r="BC4" s="16">
         <v>48</v>
       </c>
-      <c r="BD4" s="26">
+      <c r="BD4" s="16">
         <v>49</v>
       </c>
-      <c r="BE4" s="26">
+      <c r="BE4" s="16">
         <v>50</v>
       </c>
-      <c r="BF4" s="26">
+      <c r="BF4" s="16">
         <v>51</v>
       </c>
-      <c r="BG4" s="26">
+      <c r="BG4" s="16">
         <v>52</v>
       </c>
-      <c r="BH4" s="26">
+      <c r="BH4" s="16">
         <v>53</v>
       </c>
-      <c r="BI4" s="26">
+      <c r="BI4" s="16">
         <v>54</v>
       </c>
-      <c r="BJ4" s="26">
+      <c r="BJ4" s="16">
         <v>55</v>
       </c>
-      <c r="BK4" s="26">
+      <c r="BK4" s="16">
         <v>56</v>
       </c>
-      <c r="BL4" s="26">
+      <c r="BL4" s="16">
         <v>57</v>
       </c>
-      <c r="BM4" s="26">
+      <c r="BM4" s="16">
         <v>58</v>
       </c>
-      <c r="BN4" s="26">
+      <c r="BN4" s="16">
         <v>59</v>
       </c>
-      <c r="BO4" s="26">
+      <c r="BO4" s="16">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:67" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="38"/>
-      <c r="B5" s="39" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="17">
         <v>1</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="17">
         <v>1</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="17">
         <v>1</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="17">
         <v>4</v>
       </c>
-      <c r="G5" s="28">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13"/>
+      <c r="G5" s="18">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10"/>
       <c r="I5" s="3"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:67" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="38"/>
-      <c r="B6" s="39" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="17">
         <v>1</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="17">
         <v>1</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="17">
         <v>1</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="17">
         <v>6</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="18">
         <v>1</v>
       </c>
-      <c r="H6" s="13"/>
+      <c r="H6" s="10"/>
       <c r="I6" s="3"/>
       <c r="K6" s="3"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="1:67" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="38"/>
-      <c r="B7" s="39" t="s">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="17">
         <v>1</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="17">
         <v>1</v>
       </c>
-      <c r="E7" s="27">
-        <v>2</v>
-      </c>
-      <c r="F7" s="27">
+      <c r="E7" s="17">
+        <v>2</v>
+      </c>
+      <c r="F7" s="17">
         <v>5</v>
       </c>
-      <c r="G7" s="28">
-        <v>0.2</v>
-      </c>
-      <c r="H7" s="13"/>
+      <c r="G7" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="10"/>
       <c r="I7" s="3"/>
       <c r="K7" s="3"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="1:67" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="38"/>
-      <c r="B8" s="39" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="27">
-        <v>2</v>
-      </c>
-      <c r="D8" s="27">
-        <v>2</v>
-      </c>
-      <c r="E8" s="27">
-        <v>2</v>
-      </c>
-      <c r="F8" s="27">
-        <v>2</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="C8" s="17">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17">
+        <v>2</v>
+      </c>
+      <c r="E8" s="17">
+        <v>2</v>
+      </c>
+      <c r="F8" s="17">
+        <v>2</v>
+      </c>
+      <c r="G8" s="18">
         <v>1</v>
       </c>
       <c r="K8" s="3"/>
@@ -1525,24 +1518,24 @@
       <c r="Q8" s="3"/>
     </row>
     <row r="9" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39" t="s">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="27">
-        <v>2</v>
-      </c>
-      <c r="D9" s="27">
-        <v>2</v>
-      </c>
-      <c r="E9" s="27">
-        <v>2</v>
-      </c>
-      <c r="F9" s="27">
-        <v>2</v>
-      </c>
-      <c r="G9" s="28">
-        <v>0.2</v>
+      <c r="C9" s="17">
+        <v>2</v>
+      </c>
+      <c r="D9" s="17">
+        <v>2</v>
+      </c>
+      <c r="E9" s="17">
+        <v>2</v>
+      </c>
+      <c r="F9" s="17">
+        <v>2</v>
+      </c>
+      <c r="G9" s="18">
+        <v>1</v>
       </c>
       <c r="K9" s="3"/>
       <c r="M9" s="3"/>
@@ -1550,117 +1543,117 @@
       <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="38"/>
-      <c r="B10" s="39" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="27">
-        <v>2</v>
-      </c>
-      <c r="D10" s="27">
-        <v>2</v>
-      </c>
-      <c r="E10" s="27">
-        <v>2</v>
-      </c>
-      <c r="F10" s="27">
-        <v>2</v>
-      </c>
-      <c r="G10" s="28">
-        <v>0</v>
+      <c r="C10" s="17">
+        <v>2</v>
+      </c>
+      <c r="D10" s="17">
+        <v>2</v>
+      </c>
+      <c r="E10" s="17">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17">
+        <v>2</v>
+      </c>
+      <c r="G10" s="18">
+        <v>1</v>
       </c>
       <c r="K10" s="3"/>
       <c r="M10" s="3"/>
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="38"/>
-      <c r="B11" s="39" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="27">
-        <v>2</v>
-      </c>
-      <c r="D11" s="27">
-        <v>2</v>
-      </c>
-      <c r="E11" s="27">
-        <v>2</v>
-      </c>
-      <c r="F11" s="27">
-        <v>2</v>
-      </c>
-      <c r="G11" s="28">
-        <v>0</v>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="17">
+        <v>2</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3</v>
+      </c>
+      <c r="F11" s="17">
+        <v>2</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.2</v>
       </c>
       <c r="M11" s="3"/>
       <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="38"/>
-      <c r="B12" s="39" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="27">
-        <v>2</v>
-      </c>
-      <c r="D12" s="27">
+      <c r="C12" s="17">
+        <v>2</v>
+      </c>
+      <c r="D12" s="17">
         <v>3</v>
       </c>
-      <c r="E12" s="27">
-        <v>2</v>
-      </c>
-      <c r="F12" s="27">
-        <v>0</v>
-      </c>
-      <c r="G12" s="28">
+      <c r="E12" s="17">
+        <v>3</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
         <v>0</v>
       </c>
       <c r="M12" s="3"/>
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="17">
         <v>3</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="17">
         <v>3</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="17">
         <v>3</v>
       </c>
-      <c r="F13" s="27">
-        <v>0</v>
-      </c>
-      <c r="G13" s="28">
-        <v>0</v>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0.5</v>
       </c>
       <c r="M13" s="3"/>
       <c r="O13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
     <row r="14" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="27">
-        <v>4</v>
-      </c>
-      <c r="D14" s="27">
+      <c r="C14" s="17">
+        <v>3</v>
+      </c>
+      <c r="D14" s="17">
         <v>7</v>
       </c>
-      <c r="E14" s="27">
-        <v>0</v>
-      </c>
-      <c r="F14" s="27">
-        <v>0</v>
-      </c>
-      <c r="G14" s="28">
+      <c r="E14" s="17">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
         <v>0</v>
       </c>
       <c r="M14" s="3"/>
@@ -1669,23 +1662,23 @@
       <c r="S14" s="3"/>
     </row>
     <row r="15" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="38"/>
-      <c r="B15" s="39" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="29">
-        <v>2</v>
-      </c>
-      <c r="D15" s="27">
+      <c r="C15" s="19">
+        <v>2</v>
+      </c>
+      <c r="D15" s="17">
         <v>4</v>
       </c>
-      <c r="E15" s="27">
-        <v>2</v>
-      </c>
-      <c r="F15" s="27">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
+      <c r="E15" s="17">
+        <v>2</v>
+      </c>
+      <c r="F15" s="17">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
         <v>0</v>
       </c>
       <c r="M15" s="3"/>
@@ -1694,162 +1687,162 @@
       <c r="S15" s="3"/>
     </row>
     <row r="16" spans="1:67" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="38"/>
-      <c r="B16" s="39" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="27">
-        <v>2</v>
-      </c>
-      <c r="D16" s="27">
-        <v>2</v>
-      </c>
-      <c r="E16" s="27">
-        <v>2</v>
-      </c>
-      <c r="F16" s="27">
-        <v>2</v>
-      </c>
-      <c r="G16" s="28">
-        <v>0</v>
+      <c r="C16" s="17">
+        <v>2</v>
+      </c>
+      <c r="D16" s="17">
+        <v>2</v>
+      </c>
+      <c r="E16" s="17">
+        <v>2</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2</v>
+      </c>
+      <c r="G16" s="18">
+        <v>1</v>
       </c>
       <c r="Q16" s="3"/>
     </row>
     <row r="17" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="38"/>
-      <c r="B17" s="39" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="27">
-        <v>2</v>
-      </c>
-      <c r="D17" s="27">
-        <v>2</v>
-      </c>
-      <c r="E17" s="27">
-        <v>2</v>
-      </c>
-      <c r="F17" s="27">
-        <v>2</v>
-      </c>
-      <c r="G17" s="28">
-        <v>0</v>
+      <c r="C17" s="17">
+        <v>2</v>
+      </c>
+      <c r="D17" s="17">
+        <v>2</v>
+      </c>
+      <c r="E17" s="17">
+        <v>2</v>
+      </c>
+      <c r="F17" s="17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0.8</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="S17" s="3"/>
       <c r="U17" s="3"/>
     </row>
     <row r="18" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="38"/>
-      <c r="B18" s="39" t="s">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="27">
-        <v>2</v>
-      </c>
-      <c r="D18" s="27">
+      <c r="C18" s="17">
+        <v>2</v>
+      </c>
+      <c r="D18" s="17">
         <v>5</v>
       </c>
-      <c r="E18" s="27">
-        <v>2</v>
-      </c>
-      <c r="F18" s="27">
-        <v>0</v>
-      </c>
-      <c r="G18" s="28">
-        <v>0</v>
+      <c r="E18" s="17">
+        <v>2</v>
+      </c>
+      <c r="F18" s="17">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0.6</v>
       </c>
       <c r="Q18" s="3"/>
     </row>
     <row r="19" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="38"/>
-      <c r="B19" s="39" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="17">
         <v>4</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="17">
         <v>4</v>
       </c>
-      <c r="E19" s="27">
-        <v>0</v>
-      </c>
-      <c r="F19" s="27">
-        <v>0</v>
-      </c>
-      <c r="G19" s="28">
-        <v>0</v>
+      <c r="E19" s="17">
+        <v>0</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0</v>
+      </c>
+      <c r="G19" s="18">
+        <v>1</v>
       </c>
       <c r="O19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="S19" s="3"/>
     </row>
     <row r="20" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="38"/>
-      <c r="B20" s="39" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="27">
-        <v>2</v>
-      </c>
-      <c r="D20" s="27">
+      <c r="C20" s="17">
+        <v>2</v>
+      </c>
+      <c r="D20" s="17">
         <v>5</v>
       </c>
-      <c r="E20" s="27">
-        <v>2</v>
-      </c>
-      <c r="F20" s="27">
-        <v>0</v>
-      </c>
-      <c r="G20" s="28">
-        <v>0</v>
+      <c r="E20" s="17">
+        <v>2</v>
+      </c>
+      <c r="F20" s="17">
+        <v>0</v>
+      </c>
+      <c r="G20" s="18">
+        <v>0.1</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="S20" s="3"/>
       <c r="U20" s="3"/>
     </row>
     <row r="21" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="38"/>
-      <c r="B21" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="27">
+      <c r="A21" s="28"/>
+      <c r="B21" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="17">
         <v>3</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="17">
         <v>3</v>
       </c>
-      <c r="E21" s="27">
-        <v>0</v>
-      </c>
-      <c r="F21" s="27">
-        <v>0</v>
-      </c>
-      <c r="G21" s="28">
+      <c r="E21" s="17">
+        <v>0</v>
+      </c>
+      <c r="F21" s="17">
+        <v>0</v>
+      </c>
+      <c r="G21" s="18">
         <v>0</v>
       </c>
       <c r="S21" s="3"/>
       <c r="U21" s="3"/>
     </row>
     <row r="22" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="38"/>
-      <c r="B22" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="27">
+      <c r="A22" s="28"/>
+      <c r="B22" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="17">
         <v>4</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="17">
         <v>4</v>
       </c>
-      <c r="E22" s="27">
-        <v>0</v>
-      </c>
-      <c r="F22" s="27">
-        <v>0</v>
-      </c>
-      <c r="G22" s="28">
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+      <c r="F22" s="17">
+        <v>0</v>
+      </c>
+      <c r="G22" s="18">
         <v>0</v>
       </c>
       <c r="S22" s="3"/>
@@ -1861,48 +1854,48 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="27">
-        <v>3</v>
-      </c>
-      <c r="D23" s="27">
-        <v>3</v>
-      </c>
-      <c r="E23" s="27">
-        <v>0</v>
-      </c>
-      <c r="F23" s="27">
-        <v>0</v>
-      </c>
-      <c r="G23" s="28">
-        <v>0</v>
+      <c r="A23" s="28"/>
+      <c r="B23" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="17">
+        <v>2</v>
+      </c>
+      <c r="D23" s="17">
+        <v>2</v>
+      </c>
+      <c r="E23" s="17">
+        <v>0</v>
+      </c>
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18">
+        <v>1</v>
       </c>
       <c r="S23" s="3"/>
       <c r="U23" s="3"/>
       <c r="W23" s="3"/>
     </row>
     <row r="24" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="27">
-        <v>4</v>
-      </c>
-      <c r="D24" s="27">
-        <v>4</v>
-      </c>
-      <c r="E24" s="27">
-        <v>0</v>
-      </c>
-      <c r="F24" s="27">
-        <v>0</v>
-      </c>
-      <c r="G24" s="28">
-        <v>0</v>
+      <c r="A24" s="28"/>
+      <c r="B24" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="17">
+        <v>2</v>
+      </c>
+      <c r="D24" s="17">
+        <v>2</v>
+      </c>
+      <c r="E24" s="17">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17">
+        <v>0</v>
+      </c>
+      <c r="G24" s="18">
+        <v>1</v>
       </c>
       <c r="U24" s="3"/>
       <c r="W24" s="3"/>
@@ -1915,24 +1908,24 @@
       </c>
     </row>
     <row r="25" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="27">
-        <v>4</v>
-      </c>
-      <c r="D25" s="27">
-        <v>4</v>
-      </c>
-      <c r="E25" s="27">
-        <v>0</v>
-      </c>
-      <c r="F25" s="27">
-        <v>0</v>
-      </c>
-      <c r="G25" s="28">
-        <v>0</v>
+      <c r="A25" s="28"/>
+      <c r="B25" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="17">
+        <v>2</v>
+      </c>
+      <c r="D25" s="17">
+        <v>2</v>
+      </c>
+      <c r="E25" s="17">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17">
+        <v>0</v>
+      </c>
+      <c r="G25" s="18">
+        <v>1</v>
       </c>
       <c r="U25" s="3"/>
       <c r="W25" s="3"/>
@@ -1949,24 +1942,24 @@
       </c>
     </row>
     <row r="26" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="27">
-        <v>4</v>
-      </c>
-      <c r="D26" s="27">
-        <v>4</v>
-      </c>
-      <c r="E26" s="27">
-        <v>0</v>
-      </c>
-      <c r="F26" s="27">
-        <v>0</v>
-      </c>
-      <c r="G26" s="28">
-        <v>0</v>
+      <c r="A26" s="28"/>
+      <c r="B26" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="17">
+        <v>2</v>
+      </c>
+      <c r="D26" s="17">
+        <v>2</v>
+      </c>
+      <c r="E26" s="17">
+        <v>0</v>
+      </c>
+      <c r="F26" s="17">
+        <v>0</v>
+      </c>
+      <c r="G26" s="18">
+        <v>1</v>
       </c>
       <c r="U26" s="3"/>
       <c r="W26" s="3"/>
@@ -1980,23 +1973,23 @@
       <c r="AA26" s="3"/>
     </row>
     <row r="27" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="27">
+      <c r="A27" s="28"/>
+      <c r="B27" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="17">
         <v>4</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="17">
         <v>5</v>
       </c>
-      <c r="E27" s="27">
-        <v>0</v>
-      </c>
-      <c r="F27" s="27">
-        <v>0</v>
-      </c>
-      <c r="G27" s="28">
+      <c r="E27" s="17">
+        <v>0</v>
+      </c>
+      <c r="F27" s="17">
+        <v>0</v>
+      </c>
+      <c r="G27" s="18">
         <v>0</v>
       </c>
       <c r="W27" s="3"/>
@@ -2014,23 +2007,23 @@
       <c r="AC27" s="3"/>
     </row>
     <row r="28" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="27">
+      <c r="A28" s="28"/>
+      <c r="B28" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="17">
         <v>3</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="17">
         <v>5</v>
       </c>
-      <c r="E28" s="27">
-        <v>0</v>
-      </c>
-      <c r="F28" s="27">
-        <v>0</v>
-      </c>
-      <c r="G28" s="28">
+      <c r="E28" s="17">
+        <v>0</v>
+      </c>
+      <c r="F28" s="17">
+        <v>0</v>
+      </c>
+      <c r="G28" s="18">
         <v>0</v>
       </c>
       <c r="W28" s="3"/>
@@ -2043,23 +2036,23 @@
       </c>
     </row>
     <row r="29" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="27">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="17">
         <v>4</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="17">
         <v>6</v>
       </c>
-      <c r="E29" s="27">
-        <v>0</v>
-      </c>
-      <c r="F29" s="27">
-        <v>0</v>
-      </c>
-      <c r="G29" s="28">
+      <c r="E29" s="17">
+        <v>0</v>
+      </c>
+      <c r="F29" s="17">
+        <v>0</v>
+      </c>
+      <c r="G29" s="18">
         <v>0</v>
       </c>
       <c r="V29" s="1" t="s">
@@ -2080,23 +2073,23 @@
       <c r="AC29" s="3"/>
     </row>
     <row r="30" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="30">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="20">
         <v>4</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="17">
         <v>6</v>
       </c>
-      <c r="E30" s="27">
-        <v>0</v>
-      </c>
-      <c r="F30" s="27">
-        <v>0</v>
-      </c>
-      <c r="G30" s="28">
+      <c r="E30" s="17">
+        <v>0</v>
+      </c>
+      <c r="F30" s="17">
+        <v>0</v>
+      </c>
+      <c r="G30" s="18">
         <v>0</v>
       </c>
       <c r="W30" s="3"/>
@@ -2161,24 +2154,24 @@
       </c>
     </row>
     <row r="31" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="27">
-        <v>4</v>
-      </c>
-      <c r="D31" s="27">
-        <v>6</v>
-      </c>
-      <c r="E31" s="27">
-        <v>0</v>
-      </c>
-      <c r="F31" s="27">
-        <v>0</v>
-      </c>
-      <c r="G31" s="28">
-        <v>0</v>
+      <c r="A31" s="28"/>
+      <c r="B31" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="17">
+        <v>2</v>
+      </c>
+      <c r="D31" s="17">
+        <v>2</v>
+      </c>
+      <c r="E31" s="17">
+        <v>0</v>
+      </c>
+      <c r="F31" s="17">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18">
+        <v>1</v>
       </c>
       <c r="W31" s="3"/>
       <c r="X31" s="1" t="s">
@@ -2190,24 +2183,24 @@
       </c>
     </row>
     <row r="32" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="38"/>
-      <c r="B32" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="27">
-        <v>4</v>
-      </c>
-      <c r="D32" s="27">
-        <v>5</v>
-      </c>
-      <c r="E32" s="27">
-        <v>0</v>
-      </c>
-      <c r="F32" s="27">
-        <v>0</v>
-      </c>
-      <c r="G32" s="28">
-        <v>0</v>
+      <c r="A32" s="28"/>
+      <c r="B32" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="17">
+        <v>2</v>
+      </c>
+      <c r="D32" s="17">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17">
+        <v>0</v>
+      </c>
+      <c r="F32" s="17">
+        <v>0</v>
+      </c>
+      <c r="G32" s="18">
+        <v>1</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>18</v>
@@ -2227,23 +2220,23 @@
       <c r="AC32" s="3"/>
     </row>
     <row r="33" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="30">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="20">
         <v>5</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="17">
         <v>5</v>
       </c>
-      <c r="E33" s="27">
-        <v>0</v>
-      </c>
-      <c r="F33" s="27">
-        <v>0</v>
-      </c>
-      <c r="G33" s="28">
+      <c r="E33" s="17">
+        <v>0</v>
+      </c>
+      <c r="F33" s="17">
+        <v>0</v>
+      </c>
+      <c r="G33" s="18">
         <v>0</v>
       </c>
       <c r="W33" s="3"/>
@@ -2308,23 +2301,23 @@
       </c>
     </row>
     <row r="34" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="27">
+      <c r="A34" s="28"/>
+      <c r="B34" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="17">
         <v>5</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="17">
         <v>5</v>
       </c>
-      <c r="E34" s="27">
-        <v>0</v>
-      </c>
-      <c r="F34" s="27">
-        <v>0</v>
-      </c>
-      <c r="G34" s="28">
+      <c r="E34" s="17">
+        <v>0</v>
+      </c>
+      <c r="F34" s="17">
+        <v>0</v>
+      </c>
+      <c r="G34" s="18">
         <v>0</v>
       </c>
       <c r="W34" s="3"/>
@@ -2337,24 +2330,24 @@
       </c>
     </row>
     <row r="35" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="38"/>
-      <c r="B35" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="27">
-        <v>5</v>
-      </c>
-      <c r="D35" s="27">
-        <v>5</v>
-      </c>
-      <c r="E35" s="27">
-        <v>0</v>
-      </c>
-      <c r="F35" s="27">
-        <v>0</v>
-      </c>
-      <c r="G35" s="28">
-        <v>0</v>
+      <c r="A35" s="28"/>
+      <c r="B35" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="17">
+        <v>2</v>
+      </c>
+      <c r="D35" s="17">
+        <v>2</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0</v>
+      </c>
+      <c r="G35" s="18">
+        <v>1</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>18</v>
@@ -2374,23 +2367,23 @@
       <c r="AC35" s="3"/>
     </row>
     <row r="36" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="30">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="20">
         <v>6</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="17">
         <v>6</v>
       </c>
-      <c r="E36" s="27">
-        <v>0</v>
-      </c>
-      <c r="F36" s="27">
-        <v>0</v>
-      </c>
-      <c r="G36" s="28">
+      <c r="E36" s="17">
+        <v>0</v>
+      </c>
+      <c r="F36" s="17">
+        <v>0</v>
+      </c>
+      <c r="G36" s="18">
         <v>0</v>
       </c>
       <c r="W36" s="3"/>
@@ -2455,23 +2448,23 @@
       </c>
     </row>
     <row r="37" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="38"/>
-      <c r="B37" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="27">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="17">
         <v>6</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="17">
         <v>6</v>
       </c>
-      <c r="E37" s="27">
-        <v>0</v>
-      </c>
-      <c r="F37" s="27">
-        <v>0</v>
-      </c>
-      <c r="G37" s="28">
+      <c r="E37" s="17">
+        <v>0</v>
+      </c>
+      <c r="F37" s="17">
+        <v>0</v>
+      </c>
+      <c r="G37" s="18">
         <v>0</v>
       </c>
       <c r="W37" s="3"/>
@@ -2484,23 +2477,23 @@
       </c>
     </row>
     <row r="38" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="38"/>
-      <c r="B38" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="27">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="17">
         <v>6</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="17">
         <v>6</v>
       </c>
-      <c r="E38" s="27">
-        <v>0</v>
-      </c>
-      <c r="F38" s="27">
-        <v>0</v>
-      </c>
-      <c r="G38" s="28">
+      <c r="E38" s="17">
+        <v>0</v>
+      </c>
+      <c r="F38" s="17">
+        <v>0</v>
+      </c>
+      <c r="G38" s="18">
         <v>0</v>
       </c>
       <c r="V38" s="1" t="s">
@@ -2521,23 +2514,23 @@
       <c r="AC38" s="3"/>
     </row>
     <row r="39" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="38"/>
-      <c r="B39" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="30">
+      <c r="A39" s="28"/>
+      <c r="B39" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="20">
         <v>6</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="17">
         <v>6</v>
       </c>
-      <c r="E39" s="27">
-        <v>0</v>
-      </c>
-      <c r="F39" s="27">
-        <v>0</v>
-      </c>
-      <c r="G39" s="28">
+      <c r="E39" s="17">
+        <v>0</v>
+      </c>
+      <c r="F39" s="17">
+        <v>0</v>
+      </c>
+      <c r="G39" s="18">
         <v>0</v>
       </c>
       <c r="W39" s="3"/>
@@ -2619,7 +2612,7 @@
       <formula>H$4=Zeitraum_ausgewählt</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L5:BO5 N6:BO7 S8:BO9 H8:J10 Q10:BO10 P11:BO11 H11:K13 Q12:BO12 R13:BO13 H14:L14 T14:BO15 H15:K15 S16:BO16 H16:O18 W17:BO17 S18:BO18 H19:N19 T19:BO19 H20:P20 V20:BO20 H21:Q21 W21:BO21 Z22:BO22 H22:R23 X23:BO23 AA24:BO24 H24:T26 AC25:BO25 AB26:BO26 AD27:BO27 H27:U29 AA28:BO28 AD29:BO29 H30:V30 BA30:BO30 H31:U32 AA31:BO31 AD32:BO32 H33:V33 BA33:BO33 H34:U35 AA34:BO34 AD35:BO35 H36:V36 BA36:BO36 H37:U38 AA37:BO37 AD38:BO38 H39:V39 BA39:BO39">
+  <conditionalFormatting sqref="L5:BO5 N6:BO7 S8:BO9 H8:J10 Q10:BO10 P11:BO11 H11:K13 Q12:BO12 R13:BO13 H14:L14 T14:BO15 H15:K15 S16:BO16 H16:O18 W17:BO17 S18:BO18 H19:N19 T19:BO19 H20:P20 V20:BO20 H21:Q21 W21:BO21 Z22:BO22 H22:R23 X23:BO23 AA24:BO24 H24:T26 AC25:BO25 AB26:BO26 AD27:BO27 H27:U29 AA28:BO28 AD29:BO29 H30:V30 BA30:BO30 AA31:BO31 H31:U32 AD32:BO32 H33:V33 BA33:BO33 AA34:BO34 H34:U35 AD35:BO35 H36:V36 BA36:BO36 AA37:BO37 H37:U38 AD38:BO38 H39:V39 BA39:BO39">
     <cfRule type="expression" dxfId="7" priority="25">
       <formula>ProzentAbgeschlossen</formula>
     </cfRule>
